--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/93.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/93.xlsx
@@ -426,13 +426,13 @@
         <v>-1.2196636575695</v>
       </c>
       <c r="E2">
-        <v>-7.392278599334594</v>
+        <v>-8.633631932212596</v>
       </c>
       <c r="F2">
-        <v>-0.251912473010657</v>
+        <v>-1.890996425990816</v>
       </c>
       <c r="G2">
-        <v>-10.10840176332682</v>
+        <v>-10.91553042350934</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.173728667008612</v>
       </c>
       <c r="E3">
-        <v>-7.914075610552078</v>
+        <v>-9.596936073315979</v>
       </c>
       <c r="F3">
-        <v>-0.2591946508486674</v>
+        <v>-1.873213034587517</v>
       </c>
       <c r="G3">
-        <v>-9.844745277814884</v>
+        <v>-10.42277718401032</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.181812156828836</v>
       </c>
       <c r="E4">
-        <v>-8.173003417387187</v>
+        <v>-10.2945800520267</v>
       </c>
       <c r="F4">
-        <v>-0.338296282509395</v>
+        <v>-1.775275156554531</v>
       </c>
       <c r="G4">
-        <v>-9.468726261218315</v>
+        <v>-10.48211940856633</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.252300717176059</v>
       </c>
       <c r="E5">
-        <v>-8.683096679091305</v>
+        <v>-11.14133677693274</v>
       </c>
       <c r="F5">
-        <v>0.2842383880424894</v>
+        <v>-1.653621119779396</v>
       </c>
       <c r="G5">
-        <v>-10.26234301276952</v>
+        <v>-10.12680359657729</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.378300914013123</v>
       </c>
       <c r="E6">
-        <v>-10.93024150492569</v>
+        <v>-12.07715081227709</v>
       </c>
       <c r="F6">
-        <v>0.3460586189460137</v>
+        <v>-1.551589450041775</v>
       </c>
       <c r="G6">
-        <v>-9.570776351168048</v>
+        <v>-10.10431594804173</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.549058698596111</v>
       </c>
       <c r="E7">
-        <v>-10.13093937261713</v>
+        <v>-13.28593881515711</v>
       </c>
       <c r="F7">
-        <v>0.1195680604073785</v>
+        <v>-1.174112364994874</v>
       </c>
       <c r="G7">
-        <v>-9.306780468859262</v>
+        <v>-9.82325362834084</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.742820849763239</v>
       </c>
       <c r="E8">
-        <v>-11.31291008997274</v>
+        <v>-14.03443886654036</v>
       </c>
       <c r="F8">
-        <v>0.3755161921569669</v>
+        <v>-1.127864612896577</v>
       </c>
       <c r="G8">
-        <v>-8.275905775729157</v>
+        <v>-9.929873826697316</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.930859396584926</v>
       </c>
       <c r="E9">
-        <v>-12.34837627784501</v>
+        <v>-15.09977910347213</v>
       </c>
       <c r="F9">
-        <v>0.6686265423309468</v>
+        <v>-0.7718886321567403</v>
       </c>
       <c r="G9">
-        <v>-8.562574669439465</v>
+        <v>-9.105284506689435</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.080594505452076</v>
       </c>
       <c r="E10">
-        <v>-13.38210642338351</v>
+        <v>-15.74215629908336</v>
       </c>
       <c r="F10">
-        <v>0.8116035844215442</v>
+        <v>-0.6700541138609859</v>
       </c>
       <c r="G10">
-        <v>-8.404914414326726</v>
+        <v>-9.081787805369416</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.163492248302929</v>
       </c>
       <c r="E11">
-        <v>-14.53998436184379</v>
+        <v>-16.51529320004549</v>
       </c>
       <c r="F11">
-        <v>1.168760817077773</v>
+        <v>-0.6335032305798605</v>
       </c>
       <c r="G11">
-        <v>-7.543016248739541</v>
+        <v>-8.400687618833713</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.162255516509518</v>
       </c>
       <c r="E12">
-        <v>-15.78036584327178</v>
+        <v>-17.61069022733504</v>
       </c>
       <c r="F12">
-        <v>1.128990898069369</v>
+        <v>-0.693967424045002</v>
       </c>
       <c r="G12">
-        <v>-6.323135395563494</v>
+        <v>-7.840077211294775</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.070469903343167</v>
       </c>
       <c r="E13">
-        <v>-16.12148570222525</v>
+        <v>-18.99767591531816</v>
       </c>
       <c r="F13">
-        <v>1.362008991742065</v>
+        <v>-0.4125710173140099</v>
       </c>
       <c r="G13">
-        <v>-6.634205613594641</v>
+        <v>-7.6621562727827</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.893371126209579</v>
       </c>
       <c r="E14">
-        <v>-17.66135525228663</v>
+        <v>-20.03769402280245</v>
       </c>
       <c r="F14">
-        <v>1.293168347099815</v>
+        <v>-0.2169744210627823</v>
       </c>
       <c r="G14">
-        <v>-6.230795970120408</v>
+        <v>-6.848333663468571</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.641031250186609</v>
       </c>
       <c r="E15">
-        <v>-18.19716104530276</v>
+        <v>-21.17512154869927</v>
       </c>
       <c r="F15">
-        <v>1.551792933927848</v>
+        <v>-0.3545910976898641</v>
       </c>
       <c r="G15">
-        <v>-5.27471258266422</v>
+        <v>-6.215358637353154</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.327636340243339</v>
       </c>
       <c r="E16">
-        <v>-19.24714270675531</v>
+        <v>-21.91915689790833</v>
       </c>
       <c r="F16">
-        <v>2.239183801914517</v>
+        <v>-0.02688232620315731</v>
       </c>
       <c r="G16">
-        <v>-4.198349581150852</v>
+        <v>-5.662089643604427</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.9712670360745317</v>
       </c>
       <c r="E17">
-        <v>-20.23471821484099</v>
+        <v>-22.72892927596677</v>
       </c>
       <c r="F17">
-        <v>2.275395054560495</v>
+        <v>0.1031100568485579</v>
       </c>
       <c r="G17">
-        <v>-4.299074718220594</v>
+        <v>-4.920123863043805</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.5886309945719178</v>
       </c>
       <c r="E18">
-        <v>-20.50298659394564</v>
+        <v>-22.92297146227408</v>
       </c>
       <c r="F18">
-        <v>2.138918211479665</v>
+        <v>0.3647780655144769</v>
       </c>
       <c r="G18">
-        <v>-3.064448379593939</v>
+        <v>-4.645580572586923</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.1981732325328975</v>
       </c>
       <c r="E19">
-        <v>-21.65693974770395</v>
+        <v>-24.09878712044629</v>
       </c>
       <c r="F19">
-        <v>2.765038056150865</v>
+        <v>0.4219080801833505</v>
       </c>
       <c r="G19">
-        <v>-3.014729359600778</v>
+        <v>-4.248802220374117</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.1806248354866932</v>
       </c>
       <c r="E20">
-        <v>-22.47521374934432</v>
+        <v>-24.87221474620116</v>
       </c>
       <c r="F20">
-        <v>2.797594551815692</v>
+        <v>0.7742392443508698</v>
       </c>
       <c r="G20">
-        <v>-2.999670584799236</v>
+        <v>-3.453961029609677</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.5284008685983851</v>
       </c>
       <c r="E21">
-        <v>-23.95741596016045</v>
+        <v>-26.22798489786687</v>
       </c>
       <c r="F21">
-        <v>3.335499895027968</v>
+        <v>0.9534548752117372</v>
       </c>
       <c r="G21">
-        <v>-2.699508057669759</v>
+        <v>-2.814858585938918</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.8228887361654679</v>
       </c>
       <c r="E22">
-        <v>-23.97494666516256</v>
+        <v>-26.20925391479189</v>
       </c>
       <c r="F22">
-        <v>2.594528566693421</v>
+        <v>1.145709008992669</v>
       </c>
       <c r="G22">
-        <v>-2.212614634405496</v>
+        <v>-2.578513099594614</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.042323957633666</v>
       </c>
       <c r="E23">
-        <v>-24.39481141083477</v>
+        <v>-26.15824002008902</v>
       </c>
       <c r="F23">
-        <v>3.140578418210021</v>
+        <v>1.365488134833823</v>
       </c>
       <c r="G23">
-        <v>-2.293409347266679</v>
+        <v>-2.579084852660068</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.167623006438565</v>
       </c>
       <c r="E24">
-        <v>-24.16535894477197</v>
+        <v>-26.80719174922746</v>
       </c>
       <c r="F24">
-        <v>3.885830749282236</v>
+        <v>1.274826636067028</v>
       </c>
       <c r="G24">
-        <v>-2.144291448456062</v>
+        <v>-2.512150582833105</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.185227785535325</v>
       </c>
       <c r="E25">
-        <v>-24.79951278196004</v>
+        <v>-27.00425332016792</v>
       </c>
       <c r="F25">
-        <v>3.683157410308892</v>
+        <v>1.708046220383113</v>
       </c>
       <c r="G25">
-        <v>-2.092316745136178</v>
+        <v>-2.433687264891787</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.090712821603947</v>
       </c>
       <c r="E26">
-        <v>-24.45272378954818</v>
+        <v>-27.10723634817837</v>
       </c>
       <c r="F26">
-        <v>3.78738094019432</v>
+        <v>1.649407748673742</v>
       </c>
       <c r="G26">
-        <v>-1.928059138441695</v>
+        <v>-2.467574729684437</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.8908740137544834</v>
       </c>
       <c r="E27">
-        <v>-24.91200251069302</v>
+        <v>-27.2240661827458</v>
       </c>
       <c r="F27">
-        <v>3.528817652554094</v>
+        <v>1.416003635791342</v>
       </c>
       <c r="G27">
-        <v>-2.310407905299417</v>
+        <v>-2.841263656733438</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.6025194346930968</v>
       </c>
       <c r="E28">
-        <v>-24.47475242241507</v>
+        <v>-27.43922744863987</v>
       </c>
       <c r="F28">
-        <v>3.728810394611978</v>
+        <v>1.436646551469106</v>
       </c>
       <c r="G28">
-        <v>-1.955816574934411</v>
+        <v>-2.759502968373543</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.2511484543244816</v>
       </c>
       <c r="E29">
-        <v>-24.55179864570197</v>
+        <v>-27.11131895491068</v>
       </c>
       <c r="F29">
-        <v>3.378187324029032</v>
+        <v>1.518678118633535</v>
       </c>
       <c r="G29">
-        <v>-2.622292675642993</v>
+        <v>-3.003803393486968</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.1321987566768769</v>
       </c>
       <c r="E30">
-        <v>-23.76569541898372</v>
+        <v>-26.92918402547165</v>
       </c>
       <c r="F30">
-        <v>3.864274972726587</v>
+        <v>1.384709572048382</v>
       </c>
       <c r="G30">
-        <v>-2.527606190812496</v>
+        <v>-3.523015224044623</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.5166414622416071</v>
       </c>
       <c r="E31">
-        <v>-23.69442215943834</v>
+        <v>-26.18357045595915</v>
       </c>
       <c r="F31">
-        <v>4.067408883975888</v>
+        <v>1.71481232532918</v>
       </c>
       <c r="G31">
-        <v>-2.738862421636201</v>
+        <v>-3.558056637946545</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.87441857703722</v>
       </c>
       <c r="E32">
-        <v>-23.82542275104608</v>
+        <v>-26.6711533122827</v>
       </c>
       <c r="F32">
-        <v>3.768852018128501</v>
+        <v>1.448488891859527</v>
       </c>
       <c r="G32">
-        <v>-4.000000871585612</v>
+        <v>-4.224287328663562</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.184701005786793</v>
       </c>
       <c r="E33">
-        <v>-23.00643439705784</v>
+        <v>-25.98417478025413</v>
       </c>
       <c r="F33">
-        <v>3.838224474643348</v>
+        <v>1.652817308903665</v>
       </c>
       <c r="G33">
-        <v>-3.253124280449105</v>
+        <v>-4.241476471051453</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.437665366122998</v>
       </c>
       <c r="E34">
-        <v>-22.83415919130395</v>
+        <v>-25.87643632527676</v>
       </c>
       <c r="F34">
-        <v>3.610141793956533</v>
+        <v>1.455750360512468</v>
       </c>
       <c r="G34">
-        <v>-3.307357277840301</v>
+        <v>-3.870322577000424</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.628375136984388</v>
       </c>
       <c r="E35">
-        <v>-21.91484171134183</v>
+        <v>-25.23521787562515</v>
       </c>
       <c r="F35">
-        <v>3.589497221543963</v>
+        <v>1.548209416543338</v>
       </c>
       <c r="G35">
-        <v>-3.363595327077473</v>
+        <v>-4.549758413859291</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.757858690956084</v>
       </c>
       <c r="E36">
-        <v>-22.04897382428849</v>
+        <v>-24.29653812446668</v>
       </c>
       <c r="F36">
-        <v>3.317711533420251</v>
+        <v>1.825684331989477</v>
       </c>
       <c r="G36">
-        <v>-3.45535255647674</v>
+        <v>-4.922635399340455</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.833241464445824</v>
       </c>
       <c r="E37">
-        <v>-21.99857875807302</v>
+        <v>-23.76120995075291</v>
       </c>
       <c r="F37">
-        <v>3.73420803660862</v>
+        <v>1.465886264053123</v>
       </c>
       <c r="G37">
-        <v>-3.794010512602182</v>
+        <v>-4.769875511825235</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.86308493769108</v>
       </c>
       <c r="E38">
-        <v>-20.97202536170383</v>
+        <v>-23.42104117719282</v>
       </c>
       <c r="F38">
-        <v>3.732624198134467</v>
+        <v>1.559604438536248</v>
       </c>
       <c r="G38">
-        <v>-4.289088620159585</v>
+        <v>-5.024665908705754</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.860779916065388</v>
       </c>
       <c r="E39">
-        <v>-20.65869463972479</v>
+        <v>-22.75821356901814</v>
       </c>
       <c r="F39">
-        <v>3.214006561528975</v>
+        <v>1.592873330167481</v>
       </c>
       <c r="G39">
-        <v>-3.842254461901365</v>
+        <v>-4.99494519228052</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.838747559336714</v>
       </c>
       <c r="E40">
-        <v>-20.4083681335434</v>
+        <v>-22.15732280133062</v>
       </c>
       <c r="F40">
-        <v>3.472233532003665</v>
+        <v>1.765205227911085</v>
       </c>
       <c r="G40">
-        <v>-3.880828213235064</v>
+        <v>-5.359783695165646</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.808180483334854</v>
       </c>
       <c r="E41">
-        <v>-18.64986107970907</v>
+        <v>-21.46313429444215</v>
       </c>
       <c r="F41">
-        <v>3.563971908394099</v>
+        <v>1.642813944147458</v>
       </c>
       <c r="G41">
-        <v>-3.907593566783157</v>
+        <v>-5.448948455185938</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.782761822682331</v>
       </c>
       <c r="E42">
-        <v>-18.97082540410314</v>
+        <v>-21.04704066465288</v>
       </c>
       <c r="F42">
-        <v>3.448550507957627</v>
+        <v>1.666077814287679</v>
       </c>
       <c r="G42">
-        <v>-4.146902248238374</v>
+        <v>-5.424665919743994</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.773213948854771</v>
       </c>
       <c r="E43">
-        <v>-18.30500748377458</v>
+        <v>-20.15962400087676</v>
       </c>
       <c r="F43">
-        <v>3.830076652869412</v>
+        <v>1.61343506583977</v>
       </c>
       <c r="G43">
-        <v>-4.714833183610794</v>
+        <v>-5.455175081035744</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.789405035243455</v>
       </c>
       <c r="E44">
-        <v>-17.56490937890146</v>
+        <v>-19.38995918458219</v>
       </c>
       <c r="F44">
-        <v>3.313806609483454</v>
+        <v>1.581221514279703</v>
       </c>
       <c r="G44">
-        <v>-4.519332796394457</v>
+        <v>-6.026724508411446</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.837461169432671</v>
       </c>
       <c r="E45">
-        <v>-17.30749749419991</v>
+        <v>-19.20258705566255</v>
       </c>
       <c r="F45">
-        <v>3.170658095340477</v>
+        <v>1.647422980376634</v>
       </c>
       <c r="G45">
-        <v>-3.804967807651085</v>
+        <v>-5.842285846027657</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.92015823554869</v>
       </c>
       <c r="E46">
-        <v>-15.95605083552335</v>
+        <v>-18.67870097914868</v>
       </c>
       <c r="F46">
-        <v>3.601167261514603</v>
+        <v>1.473427720888209</v>
       </c>
       <c r="G46">
-        <v>-4.451516094895699</v>
+        <v>-6.302006639587614</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.039618441234715</v>
       </c>
       <c r="E47">
-        <v>-16.18133763062735</v>
+        <v>-17.16251719327279</v>
       </c>
       <c r="F47">
-        <v>3.162805172361938</v>
+        <v>1.562909624473418</v>
       </c>
       <c r="G47">
-        <v>-4.246358563436835</v>
+        <v>-6.862040072571915</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.191187467608628</v>
       </c>
       <c r="E48">
-        <v>-15.0325801442364</v>
+        <v>-17.01842983278052</v>
       </c>
       <c r="F48">
-        <v>3.589240427649095</v>
+        <v>1.352303839250866</v>
       </c>
       <c r="G48">
-        <v>-5.029268651419887</v>
+        <v>-6.584418714242111</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.366873410512298</v>
       </c>
       <c r="E49">
-        <v>-14.63082755315176</v>
+        <v>-17.09813826452663</v>
       </c>
       <c r="F49">
-        <v>3.399552576082037</v>
+        <v>1.420109024639616</v>
       </c>
       <c r="G49">
-        <v>-5.023394476089882</v>
+        <v>-7.020034502992318</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.557259634157369</v>
       </c>
       <c r="E50">
-        <v>-13.80227020027112</v>
+        <v>-15.65285810238822</v>
       </c>
       <c r="F50">
-        <v>3.122952416613253</v>
+        <v>1.376480570268972</v>
       </c>
       <c r="G50">
-        <v>-4.714624324043505</v>
+        <v>-7.006769309724872</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.750623167951632</v>
       </c>
       <c r="E51">
-        <v>-14.0921726571668</v>
+        <v>-15.68613778473407</v>
       </c>
       <c r="F51">
-        <v>2.978531530139576</v>
+        <v>1.630284058812713</v>
       </c>
       <c r="G51">
-        <v>-5.67021167002738</v>
+        <v>-7.364386493070978</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.941187897034023</v>
       </c>
       <c r="E52">
-        <v>-13.20662078527553</v>
+        <v>-14.24023879410826</v>
       </c>
       <c r="F52">
-        <v>2.83856394682335</v>
+        <v>1.476631846002238</v>
       </c>
       <c r="G52">
-        <v>-5.715367108475276</v>
+        <v>-7.302626719023602</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.127135390413028</v>
       </c>
       <c r="E53">
-        <v>-13.00333355055915</v>
+        <v>-13.72480865585174</v>
       </c>
       <c r="F53">
-        <v>2.817680804598774</v>
+        <v>1.453364662392405</v>
       </c>
       <c r="G53">
-        <v>-5.60973116082965</v>
+        <v>-7.523049274106706</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.308879533073274</v>
       </c>
       <c r="E54">
-        <v>-12.92105012779165</v>
+        <v>-13.04355740224011</v>
       </c>
       <c r="F54">
-        <v>2.862326494140056</v>
+        <v>1.342466147975219</v>
       </c>
       <c r="G54">
-        <v>-5.805453461336231</v>
+        <v>-7.901239124830785</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.4945304634856</v>
       </c>
       <c r="E55">
-        <v>-12.254297734915</v>
+        <v>-12.62039500677598</v>
       </c>
       <c r="F55">
-        <v>3.023374371122725</v>
+        <v>1.259720528109576</v>
       </c>
       <c r="G55">
-        <v>-5.98224525281265</v>
+        <v>-8.020727683276858</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.690568698785476</v>
       </c>
       <c r="E56">
-        <v>-10.68507328720973</v>
+        <v>-11.88192080753087</v>
       </c>
       <c r="F56">
-        <v>2.609478941579146</v>
+        <v>0.9918397639226607</v>
       </c>
       <c r="G56">
-        <v>-5.932163339321323</v>
+        <v>-8.075895327231674</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.904767531437827</v>
       </c>
       <c r="E57">
-        <v>-11.32327650543951</v>
+        <v>-11.61144707321274</v>
       </c>
       <c r="F57">
-        <v>3.193141643387261</v>
+        <v>1.107332403955773</v>
       </c>
       <c r="G57">
-        <v>-5.984490493161006</v>
+        <v>-8.463729268475324</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.146388706045867</v>
       </c>
       <c r="E58">
-        <v>-9.774872106105608</v>
+        <v>-11.17231142699332</v>
       </c>
       <c r="F58">
-        <v>2.849756847169977</v>
+        <v>1.04541194059651</v>
       </c>
       <c r="G58">
-        <v>-7.334493467502731</v>
+        <v>-8.609061587628828</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.418176975057799</v>
       </c>
       <c r="E59">
-        <v>-9.922041149400908</v>
+        <v>-10.4993084510728</v>
       </c>
       <c r="F59">
-        <v>2.679350075270479</v>
+        <v>0.858977916187648</v>
       </c>
       <c r="G59">
-        <v>-6.858400694611904</v>
+        <v>-9.019214784381909</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.723993425796047</v>
       </c>
       <c r="E60">
-        <v>-8.586746329566607</v>
+        <v>-10.17848948907509</v>
       </c>
       <c r="F60">
-        <v>2.570789213663993</v>
+        <v>0.8112639537863965</v>
       </c>
       <c r="G60">
-        <v>-7.461889971315286</v>
+        <v>-9.116993696180579</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.061249363864987</v>
       </c>
       <c r="E61">
-        <v>-9.190349144249238</v>
+        <v>-9.557509638209382</v>
       </c>
       <c r="F61">
-        <v>2.861807936145904</v>
+        <v>0.7901207041973419</v>
       </c>
       <c r="G61">
-        <v>-7.058255803806217</v>
+        <v>-9.477328664646034</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.419964060103519</v>
       </c>
       <c r="E62">
-        <v>-8.161357812832369</v>
+        <v>-9.345961666167915</v>
       </c>
       <c r="F62">
-        <v>2.700301143622084</v>
+        <v>0.5948711938878872</v>
       </c>
       <c r="G62">
-        <v>-7.197826209647133</v>
+        <v>-9.557673024065251</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.789963008262087</v>
       </c>
       <c r="E63">
-        <v>-8.1109295209263</v>
+        <v>-9.037739394118415</v>
       </c>
       <c r="F63">
-        <v>2.542180717040909</v>
+        <v>0.544995192565329</v>
       </c>
       <c r="G63">
-        <v>-7.007907594366597</v>
+        <v>-9.840985805603681</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.151565045681641</v>
       </c>
       <c r="E64">
-        <v>-8.713020566686694</v>
+        <v>-8.077903184471264</v>
       </c>
       <c r="F64">
-        <v>2.388140828285924</v>
+        <v>0.5491618806014105</v>
       </c>
       <c r="G64">
-        <v>-7.823325368625897</v>
+        <v>-9.979861753383361</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.48560255544572</v>
       </c>
       <c r="E65">
-        <v>-6.634786845433091</v>
+        <v>-7.830301184918961</v>
       </c>
       <c r="F65">
-        <v>2.275080274947431</v>
+        <v>0.67935969876902</v>
       </c>
       <c r="G65">
-        <v>-7.258450309797374</v>
+        <v>-9.704057473288971</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.773769957761739</v>
       </c>
       <c r="E66">
-        <v>-7.713533648521406</v>
+        <v>-8.584644804636245</v>
       </c>
       <c r="F66">
-        <v>2.461272416074676</v>
+        <v>0.7188131814295549</v>
       </c>
       <c r="G66">
-        <v>-7.586647012346226</v>
+        <v>-9.823123091111285</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.997624217320462</v>
       </c>
       <c r="E67">
-        <v>-7.50245914257097</v>
+        <v>-8.059379861962528</v>
       </c>
       <c r="F67">
-        <v>2.432292810855138</v>
+        <v>0.3212498435995713</v>
       </c>
       <c r="G67">
-        <v>-7.433581667713844</v>
+        <v>-9.80027124370527</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.145277522173755</v>
       </c>
       <c r="E68">
-        <v>-7.050855555954414</v>
+        <v>-7.947679243381265</v>
       </c>
       <c r="F68">
-        <v>2.360146980275718</v>
+        <v>0.5310587393806301</v>
       </c>
       <c r="G68">
-        <v>-6.606641372201667</v>
+        <v>-9.751270178474664</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.206057847834775</v>
       </c>
       <c r="E69">
-        <v>-6.852942576692359</v>
+        <v>-8.314744213480937</v>
       </c>
       <c r="F69">
-        <v>2.48751675213017</v>
+        <v>0.03054175889371002</v>
       </c>
       <c r="G69">
-        <v>-7.605295560960548</v>
+        <v>-9.846499698180113</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.176695492229074</v>
       </c>
       <c r="E70">
-        <v>-7.285644898569621</v>
+        <v>-7.73960750921868</v>
       </c>
       <c r="F70">
-        <v>2.015310884368728</v>
+        <v>0.36701300076723</v>
       </c>
       <c r="G70">
-        <v>-6.925021675087932</v>
+        <v>-9.882238180887862</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.061831453251573</v>
       </c>
       <c r="E71">
-        <v>-7.318143777186404</v>
+        <v>-8.117765706766969</v>
       </c>
       <c r="F71">
-        <v>2.124352199068838</v>
+        <v>0.1387522210888122</v>
       </c>
       <c r="G71">
-        <v>-7.654043383965815</v>
+        <v>-9.214029851143076</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.867787735518606</v>
       </c>
       <c r="E72">
-        <v>-7.513755877374503</v>
+        <v>-8.364553676899606</v>
       </c>
       <c r="F72">
-        <v>1.988662305020668</v>
+        <v>0.2236689919171924</v>
       </c>
       <c r="G72">
-        <v>-7.099027802085633</v>
+        <v>-9.639040795364181</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.606855050385545</v>
       </c>
       <c r="E73">
-        <v>-7.462372346863726</v>
+        <v>-8.325060790411811</v>
       </c>
       <c r="F73">
-        <v>1.919909467323115</v>
+        <v>0.199124465772243</v>
       </c>
       <c r="G73">
-        <v>-6.89628782011814</v>
+        <v>-9.023442885247215</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.288506198841104</v>
       </c>
       <c r="E74">
-        <v>-8.840848104842268</v>
+        <v>-8.409196545430188</v>
       </c>
       <c r="F74">
-        <v>1.796767682692552</v>
+        <v>0.06569352963150704</v>
       </c>
       <c r="G74">
-        <v>-6.181032567469197</v>
+        <v>-8.740092247912212</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.924910859504467</v>
       </c>
       <c r="E75">
-        <v>-8.103698780009774</v>
+        <v>-8.908337788870732</v>
       </c>
       <c r="F75">
-        <v>1.827660816612556</v>
+        <v>0.09017841332345483</v>
       </c>
       <c r="G75">
-        <v>-6.401677035842545</v>
+        <v>-8.658875899799565</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.528008771365195</v>
       </c>
       <c r="E76">
-        <v>-8.86150202476064</v>
+        <v>-9.506981669231516</v>
       </c>
       <c r="F76">
-        <v>1.708443836736457</v>
+        <v>0.04075801407243632</v>
       </c>
       <c r="G76">
-        <v>-6.804530590718872</v>
+        <v>-8.430486657596679</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.103860724921715</v>
       </c>
       <c r="E77">
-        <v>-9.756980071718246</v>
+        <v>-9.72454764448266</v>
       </c>
       <c r="F77">
-        <v>1.922798812824079</v>
+        <v>-0.01994392083730865</v>
       </c>
       <c r="G77">
-        <v>-6.09842338711719</v>
+        <v>-8.474848429688876</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.6630953508642</v>
       </c>
       <c r="E78">
-        <v>-8.926786353575618</v>
+        <v>-10.0850505406891</v>
       </c>
       <c r="F78">
-        <v>1.724037024726755</v>
+        <v>-0.1006940036296073</v>
       </c>
       <c r="G78">
-        <v>-5.53187353563347</v>
+        <v>-7.746641273123421</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.211251318440707</v>
       </c>
       <c r="E79">
-        <v>-9.154926404859776</v>
+        <v>-10.96758718115854</v>
       </c>
       <c r="F79">
-        <v>1.474264371965037</v>
+        <v>-0.07963359078083262</v>
       </c>
       <c r="G79">
-        <v>-5.113519990119704</v>
+        <v>-7.167669498875183</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.752432663490205</v>
       </c>
       <c r="E80">
-        <v>-11.16964506532278</v>
+        <v>-10.67984024094045</v>
       </c>
       <c r="F80">
-        <v>1.961440495429871</v>
+        <v>-0.09868438431041565</v>
       </c>
       <c r="G80">
-        <v>-5.594432197525726</v>
+        <v>-7.22572462634777</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.292470291258228</v>
       </c>
       <c r="E81">
-        <v>-12.09739771748563</v>
+        <v>-12.07124909898451</v>
       </c>
       <c r="F81">
-        <v>1.529511507527347</v>
+        <v>0.03612081335156469</v>
       </c>
       <c r="G81">
-        <v>-4.758944324222243</v>
+        <v>-6.992339724369788</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.830175365073976</v>
       </c>
       <c r="E82">
-        <v>-12.82362824974514</v>
+        <v>-12.66763778559591</v>
       </c>
       <c r="F82">
-        <v>1.905699652895492</v>
+        <v>-0.1793599140364623</v>
       </c>
       <c r="G82">
-        <v>-3.635018777747974</v>
+        <v>-6.639095538213796</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.371559617501016</v>
       </c>
       <c r="E83">
-        <v>-12.82321292861266</v>
+        <v>-13.64480534610157</v>
       </c>
       <c r="F83">
-        <v>1.250999476092903</v>
+        <v>-0.2115320472263895</v>
       </c>
       <c r="G83">
-        <v>-4.508727951865355</v>
+        <v>-6.120445017743231</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.922881658144209</v>
       </c>
       <c r="E84">
-        <v>-14.4276441487185</v>
+        <v>-14.97068483586248</v>
       </c>
       <c r="F84">
-        <v>1.412627210257531</v>
+        <v>-0.1866818535098071</v>
       </c>
       <c r="G84">
-        <v>-4.152272549862294</v>
+        <v>-5.806944196497756</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.490762620586881</v>
       </c>
       <c r="E85">
-        <v>-16.04224658335885</v>
+        <v>-15.71781848071986</v>
       </c>
       <c r="F85">
-        <v>1.638122071178001</v>
+        <v>-0.1839606665916108</v>
       </c>
       <c r="G85">
-        <v>-4.424956990170303</v>
+        <v>-5.939154913336324</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.089576204762603</v>
       </c>
       <c r="E86">
-        <v>-16.52219583726735</v>
+        <v>-17.00035090388354</v>
       </c>
       <c r="F86">
-        <v>1.122176747813941</v>
+        <v>-0.04272319604689225</v>
       </c>
       <c r="G86">
-        <v>-3.95011737468321</v>
+        <v>-5.503419030334926</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.7314223890477995</v>
       </c>
       <c r="E87">
-        <v>-18.32681184322993</v>
+        <v>-17.55724255079583</v>
       </c>
       <c r="F87">
-        <v>1.694131304750887</v>
+        <v>-0.2423299188950723</v>
       </c>
       <c r="G87">
-        <v>-3.077564760419692</v>
+        <v>-5.331117719555222</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.4294368678225138</v>
       </c>
       <c r="E88">
-        <v>-19.21913344958067</v>
+        <v>-18.49680693596649</v>
       </c>
       <c r="F88">
-        <v>1.384767557766578</v>
+        <v>-0.2275485309595179</v>
       </c>
       <c r="G88">
-        <v>-3.040513073182612</v>
+        <v>-5.376818803622661</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.1967047259988947</v>
       </c>
       <c r="E89">
-        <v>-20.53720905526223</v>
+        <v>-19.96624632838142</v>
       </c>
       <c r="F89">
-        <v>1.168002032536809</v>
+        <v>-0.02883810164116694</v>
       </c>
       <c r="G89">
-        <v>-1.853329185265668</v>
+        <v>-4.951165616232141</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.04039249407087058</v>
       </c>
       <c r="E90">
-        <v>-23.13203166073198</v>
+        <v>-21.71813316336398</v>
       </c>
       <c r="F90">
-        <v>1.334230519256586</v>
+        <v>-0.09717344216770936</v>
       </c>
       <c r="G90">
-        <v>-2.781777841224921</v>
+        <v>-4.655973946804145</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.03225896159748488</v>
       </c>
       <c r="E91">
-        <v>-24.18801471254891</v>
+        <v>-23.43649942974384</v>
       </c>
       <c r="F91">
-        <v>1.004064810053176</v>
+        <v>-0.235522395578866</v>
       </c>
       <c r="G91">
-        <v>-2.989363365153521</v>
+        <v>-4.421607404859905</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.01759221225517538</v>
       </c>
       <c r="E92">
-        <v>-25.44041143433963</v>
+        <v>-24.98561818142561</v>
       </c>
       <c r="F92">
-        <v>1.391021731657714</v>
+        <v>-0.4529042261563179</v>
       </c>
       <c r="G92">
-        <v>-3.196076900388689</v>
+        <v>-4.840898207681881</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.08246611147597402</v>
       </c>
       <c r="E93">
-        <v>-27.70672333043809</v>
+        <v>-26.81707223896922</v>
       </c>
       <c r="F93">
-        <v>1.242129317943726</v>
+        <v>-0.1305781860530022</v>
       </c>
       <c r="G93">
-        <v>-2.779000008979977</v>
+        <v>-4.647713550917862</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.2613488381336617</v>
       </c>
       <c r="E94">
-        <v>-28.87843146261005</v>
+        <v>-28.79913004557377</v>
       </c>
       <c r="F94">
-        <v>1.11380858031086</v>
+        <v>0.06102650768413462</v>
       </c>
       <c r="G94">
-        <v>-2.455821157535245</v>
+        <v>-4.772588075455402</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.5074516983020755</v>
       </c>
       <c r="E95">
-        <v>-30.58064589014765</v>
+        <v>-31.5605545701277</v>
       </c>
       <c r="F95">
-        <v>0.9212810852870044</v>
+        <v>-0.02005326533447819</v>
       </c>
       <c r="G95">
-        <v>-2.641309339244662</v>
+        <v>-5.169799811270333</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.8040944639678936</v>
       </c>
       <c r="E96">
-        <v>-34.34336813300449</v>
+        <v>-33.43313995602676</v>
       </c>
       <c r="F96">
-        <v>0.8068487555294751</v>
+        <v>0.1136178973530696</v>
       </c>
       <c r="G96">
-        <v>-2.881435183756897</v>
+        <v>-5.465080246014427</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.130925557633999</v>
       </c>
       <c r="E97">
-        <v>-36.42062584959676</v>
+        <v>-35.29660073664516</v>
       </c>
       <c r="F97">
-        <v>1.126136343999322</v>
+        <v>0.04519143641221927</v>
       </c>
       <c r="G97">
-        <v>-3.438703838219211</v>
+        <v>-5.713991246075759</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.470278739865559</v>
       </c>
       <c r="E98">
-        <v>-39.1792760289857</v>
+        <v>-37.99449774077451</v>
       </c>
       <c r="F98">
-        <v>0.6163830669711876</v>
+        <v>0.007648168982540083</v>
       </c>
       <c r="G98">
-        <v>-3.791814876401056</v>
+        <v>-5.845925223987669</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.796746204087694</v>
       </c>
       <c r="E99">
-        <v>-42.1435683139122</v>
+        <v>-39.81296885971671</v>
       </c>
       <c r="F99">
-        <v>0.6919964434987265</v>
+        <v>0.2450756623403372</v>
       </c>
       <c r="G99">
-        <v>-4.11080348277705</v>
+        <v>-5.838646468067645</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.096743731954958</v>
       </c>
       <c r="E100">
-        <v>-43.32970054901528</v>
+        <v>-42.2513275349462</v>
       </c>
       <c r="F100">
-        <v>0.635502614995203</v>
+        <v>0.09526955938106059</v>
       </c>
       <c r="G100">
-        <v>-4.488546896176049</v>
+        <v>-5.898865902806264</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.343490401125652</v>
       </c>
       <c r="E101">
-        <v>-45.41412878495986</v>
+        <v>-44.4980736524934</v>
       </c>
       <c r="F101">
-        <v>0.5814085668575897</v>
+        <v>0.15455250092981</v>
       </c>
       <c r="G101">
-        <v>-4.419291674407588</v>
+        <v>-6.223921879612006</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.537786946221207</v>
       </c>
       <c r="E102">
-        <v>-48.83315410123618</v>
+        <v>-47.48539964742739</v>
       </c>
       <c r="F102">
-        <v>0.368008698385395</v>
+        <v>0.2227950643072389</v>
       </c>
       <c r="G102">
-        <v>-4.867050036251062</v>
+        <v>-6.672359035049171</v>
       </c>
     </row>
   </sheetData>
